--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R2" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R3" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R4" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R5" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R6" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1187,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1308,12 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574514.1481840126</v>
+        <v>574514</v>
       </c>
       <c r="R7" t="n">
-        <v>6295950.990821189</v>
+        <v>6295951</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1378,19 +1298,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110507</v>
+        <v>110535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110535</v>
+        <v>110541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110541</v>
+        <v>110548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110548</v>
+        <v>110552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110552</v>
+        <v>110560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110563</v>
+        <v>110568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106972</v>
+        <v>106977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110568</v>
+        <v>110576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106977</v>
+        <v>106985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471459</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74465958</v>
       </c>
       <c r="B3" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74470387</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74602543</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74844683</v>
       </c>
       <c r="B6" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>75144163</v>
       </c>
       <c r="B7" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74471459</v>
+        <v>74465958</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>111175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Hepatica nobilis. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Hedera helix. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74465958</v>
+        <v>74470387</v>
       </c>
       <c r="B3" t="n">
-        <v>110586</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Hedera helix. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Goodyera repens. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74470387</v>
+        <v>74844683</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>106155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Goodyera repens. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Primula veris. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,27 +1008,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74602543</v>
+        <v>75144163</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>107516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Lycopodium annotinum. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Thymus serpyllum. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74844683</v>
+        <v>74602543</v>
       </c>
       <c r="B6" t="n">
-        <v>105644</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Primula veris. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Lycopodium annotinum. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75144163</v>
+        <v>74471459</v>
       </c>
       <c r="B7" t="n">
-        <v>106995</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Thymus serpyllum. LEG: Sven Davidsson</t>
+          <t>Smålands flora 2007: KOO: 4G9f 2203. SOM: Hepatica nobilis. LEG: Sven Davidsson</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 41999-2024 artfynd.xlsx
+++ b/artfynd/A 41999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74465958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74470387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74844683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75144163</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74602543</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,8 +1368,21 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74471459</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>